--- a/artfynd/A 31411-2026 artfynd.xlsx
+++ b/artfynd/A 31411-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136420412</v>
       </c>
       <c r="B2" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136420498</v>
       </c>
       <c r="B3" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136420507</v>
       </c>
       <c r="B4" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136420390</v>
       </c>
       <c r="B5" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136420515</v>
       </c>
       <c r="B6" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31411-2026 artfynd.xlsx
+++ b/artfynd/A 31411-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136420412</v>
       </c>
       <c r="B2" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136420498</v>
       </c>
       <c r="B3" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136420507</v>
       </c>
       <c r="B4" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136420390</v>
       </c>
       <c r="B5" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136420515</v>
       </c>
       <c r="B6" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
